--- a/processed-data/05_spe_correct_cluster/10_spatial_registration_DLPFC/ERC_SpD_spatial_registration_anno_summary_k10.xlsx
+++ b/processed-data/05_spe_correct_cluster/10_spatial_registration_DLPFC/ERC_SpD_spatial_registration_anno_summary_k10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/05_spe_correct_cluster/10_spatial_registration_DLPFC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{B4D678B6-67B0-3648-9A67-1496A4979F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36DF7396-1231-6046-AE5C-8C2299C4AAB5}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{B4D678B6-67B0-3648-9A67-1496A4979F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1CD7FD0-FDDE-D247-83F6-F10043B5FF73}"/>
   <bookViews>
     <workbookView xWindow="-28040" yWindow="-15480" windowWidth="26120" windowHeight="15680" xr2:uid="{A7EC470F-248F-D347-A61D-7621A37801B2}"/>
   </bookViews>
@@ -187,9 +187,6 @@
     <t>L3</t>
   </si>
   <si>
-    <t>L5</t>
-  </si>
-  <si>
     <t>L6a</t>
   </si>
   <si>
@@ -209,6 +206,9 @@
   </si>
   <si>
     <t>Vasc</t>
+  </si>
+  <si>
+    <t>L5_LD</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1095,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
         <v>50</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1167,7 +1167,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1236,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1259,7 +1259,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1282,7 +1282,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1305,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
